--- a/artfynd/A 31803-2021 artfynd.xlsx
+++ b/artfynd/A 31803-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31803-2021 artfynd.xlsx
+++ b/artfynd/A 31803-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>2673802</v>
       </c>
       <c r="B2" t="n">
-        <v>106706</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685928.2093939063</v>
+        <v>685928</v>
       </c>
       <c r="R2" t="n">
-        <v>6628157.00619566</v>
+        <v>6628157</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,19 +757,9 @@
           <t>2008-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,16 +794,11 @@
         <v>3926555</v>
       </c>
       <c r="B3" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685928.2093939063</v>
+        <v>685928</v>
       </c>
       <c r="R3" t="n">
-        <v>6628157.00619566</v>
+        <v>6628157</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,19 +864,9 @@
           <t>2008-06-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,6 +895,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4424031</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bolsmossen V 1000 m, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>685928</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6628157</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rimbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vid grusväg i skog (vändplan och vägren)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
